--- a/tables/table2_characteristics.xlsx
+++ b/tables/table2_characteristics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="80">
   <si>
     <t>Characteristic</t>
   </si>
@@ -49,13 +49,13 @@
     <t xml:space="preserve">   Portuguese</t>
   </si>
   <si>
+    <t xml:space="preserve">   English/Portuguese</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Spanish</t>
   </si>
   <si>
-    <t xml:space="preserve">   English/Portuguese</t>
-  </si>
-  <si>
-    <t>Database where retrieved (not mutually exclusive)</t>
+    <t>Source through which the study was first identified</t>
   </si>
   <si>
     <t xml:space="preserve">   PubMed</t>
@@ -70,6 +70,9 @@
     <t xml:space="preserve">   SciSpace</t>
   </si>
   <si>
+    <t xml:space="preserve">   LILACS</t>
+  </si>
+  <si>
     <t>Region of study (not mutually exclusive)</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
     <t xml:space="preserve">   National</t>
   </si>
   <si>
+    <t xml:space="preserve">   Not specified</t>
+  </si>
+  <si>
     <t>Spatial scale</t>
   </si>
   <si>
@@ -106,30 +112,30 @@
     <t>Study design/focus</t>
   </si>
   <si>
+    <t xml:space="preserve">   Spatial, ecological and determinant analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Descriptive/surveillance epidemiology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Clinical course, severity and mortality</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Virological, molecular or genomic</t>
   </si>
   <si>
-    <t xml:space="preserve">   Descriptive/surveillance epidemiology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Clinical course, severity and mortality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Spatial, ecological and determinant analysis</t>
+    <t xml:space="preserve">   Control, vaccines and health-system response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Diagnosis and surveillance performance</t>
   </si>
   <si>
     <t xml:space="preserve">   Seroepidemiological survey</t>
   </si>
   <si>
-    <t xml:space="preserve">   Diagnosis and surveillance performance</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Review or historical analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">   Control, vaccines and health-system response</t>
-  </si>
-  <si>
     <t xml:space="preserve">   Mathematical modelling</t>
   </si>
   <si>
@@ -151,88 +157,103 @@
     <t xml:space="preserve">   Not applicable</t>
   </si>
   <si>
-    <t>4 (3.9)</t>
-  </si>
-  <si>
-    <t>16 (15.5)</t>
-  </si>
-  <si>
-    <t>31 (30.1)</t>
-  </si>
-  <si>
-    <t>29 (28.2)</t>
-  </si>
-  <si>
-    <t>23 (22.3)</t>
-  </si>
-  <si>
-    <t>72 (69.9)</t>
-  </si>
-  <si>
-    <t>27 (26.2)</t>
-  </si>
-  <si>
-    <t>3 (2.9)</t>
-  </si>
-  <si>
-    <t>1 (1.0)</t>
-  </si>
-  <si>
-    <t>58 (56.3)</t>
-  </si>
-  <si>
-    <t>46 (44.7)</t>
-  </si>
-  <si>
-    <t>8 (7.8)</t>
-  </si>
-  <si>
-    <t>6 (5.8)</t>
-  </si>
-  <si>
-    <t>49 (47.6)</t>
-  </si>
-  <si>
-    <t>20 (19.4)</t>
-  </si>
-  <si>
-    <t>5 (4.9)</t>
-  </si>
-  <si>
-    <t>2 (1.9)</t>
-  </si>
-  <si>
-    <t>56 (54.4)</t>
-  </si>
-  <si>
-    <t>26 (25.2)</t>
-  </si>
-  <si>
-    <t>19 (18.4)</t>
-  </si>
-  <si>
-    <t>22 (21.4)</t>
-  </si>
-  <si>
-    <t>18 (17.5)</t>
-  </si>
-  <si>
-    <t>13 (12.6)</t>
-  </si>
-  <si>
-    <t>11 (10.7)</t>
-  </si>
-  <si>
-    <t>7 (6.8)</t>
-  </si>
-  <si>
-    <t>51 (49.5)</t>
-  </si>
-  <si>
-    <t>28 (27.2)</t>
-  </si>
-  <si>
-    <t>14 (13.6)</t>
+    <t>8 (2.8)</t>
+  </si>
+  <si>
+    <t>30 (10.5)</t>
+  </si>
+  <si>
+    <t>83 (29.0)</t>
+  </si>
+  <si>
+    <t>122 (42.7)</t>
+  </si>
+  <si>
+    <t>43 (15.0)</t>
+  </si>
+  <si>
+    <t>157 (54.9)</t>
+  </si>
+  <si>
+    <t>119 (41.6)</t>
+  </si>
+  <si>
+    <t>7 (2.4)</t>
+  </si>
+  <si>
+    <t>3 (1.0)</t>
+  </si>
+  <si>
+    <t>58 (20.3)</t>
+  </si>
+  <si>
+    <t>46 (16.1)</t>
+  </si>
+  <si>
+    <t>6 (2.1)</t>
+  </si>
+  <si>
+    <t>183 (64.0)</t>
+  </si>
+  <si>
+    <t>130 (45.5)</t>
+  </si>
+  <si>
+    <t>20 (7.0)</t>
+  </si>
+  <si>
+    <t>24 (8.4)</t>
+  </si>
+  <si>
+    <t>11 (3.8)</t>
+  </si>
+  <si>
+    <t>38 (13.3)</t>
+  </si>
+  <si>
+    <t>176 (61.5)</t>
+  </si>
+  <si>
+    <t>66 (23.1)</t>
+  </si>
+  <si>
+    <t>10 (3.5)</t>
+  </si>
+  <si>
+    <t>34 (11.9)</t>
+  </si>
+  <si>
+    <t>62 (21.7)</t>
+  </si>
+  <si>
+    <t>54 (18.9)</t>
+  </si>
+  <si>
+    <t>37 (12.9)</t>
+  </si>
+  <si>
+    <t>31 (10.8)</t>
+  </si>
+  <si>
+    <t>23 (8.0)</t>
+  </si>
+  <si>
+    <t>19 (6.6)</t>
+  </si>
+  <si>
+    <t>13 (4.5)</t>
+  </si>
+  <si>
+    <t>9 (3.1)</t>
+  </si>
+  <si>
+    <t>75 (26.2)</t>
+  </si>
+  <si>
+    <t>68 (23.8)</t>
+  </si>
+  <si>
+    <t>127 (44.4)</t>
   </si>
 </sst>
 </file>
@@ -564,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -585,7 +606,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -593,7 +614,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -601,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -609,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -617,7 +638,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -630,7 +651,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -638,7 +659,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -646,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -654,7 +675,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -667,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -675,7 +696,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -683,7 +704,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -691,28 +712,28 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -728,7 +749,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -736,7 +757,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -744,73 +765,73 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -818,7 +839,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -826,7 +847,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -834,7 +855,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -842,7 +863,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -850,7 +871,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -858,36 +879,36 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -895,7 +916,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -903,7 +924,23 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
